--- a/modeling/data/argentina/df_modelos.xlsx
+++ b/modeling/data/argentina/df_modelos.xlsx
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>92.60618772941794</v>
+        <v>82.18405873099108</v>
       </c>
       <c r="D2" t="n">
-        <v>167.3072570640938</v>
+        <v>135.9256601641918</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>93.91714735186156</v>
+        <v>84.49134766649186</v>
       </c>
       <c r="D3" t="n">
-        <v>170.3326896807694</v>
+        <v>139.6043810438838</v>
       </c>
     </row>
     <row r="4">
@@ -497,10 +497,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>94.16622968012587</v>
+        <v>86.43156790770843</v>
       </c>
       <c r="D4" t="n">
-        <v>171.3978443740048</v>
+        <v>146.2115685125011</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74.64604090194021</v>
+        <v>70.00524383848978</v>
       </c>
       <c r="D5" t="n">
-        <v>106.7115029819161</v>
+        <v>95.28236293754347</v>
       </c>
     </row>
     <row r="6">
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>81.59412690089145</v>
+        <v>70.64761405348716</v>
       </c>
       <c r="D6" t="n">
-        <v>130.8672322386731</v>
+        <v>98.14028208756929</v>
       </c>
     </row>
     <row r="7">
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>90.87572102779234</v>
+        <v>76.58626114315679</v>
       </c>
       <c r="D7" t="n">
-        <v>161.6580698590597</v>
+        <v>117.4579771771344</v>
       </c>
     </row>
     <row r="8">
@@ -562,10 +562,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>93.96958573675931</v>
+        <v>87.55899318300996</v>
       </c>
       <c r="D8" t="n">
-        <v>170.6904505617342</v>
+        <v>149.4355157552812</v>
       </c>
     </row>
   </sheetData>

--- a/modeling/data/argentina/df_modelos.xlsx
+++ b/modeling/data/argentina/df_modelos.xlsx
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>82.18405873099108</v>
+        <v>86.14528412419449</v>
       </c>
       <c r="D2" t="n">
-        <v>135.9256601641918</v>
+        <v>148.301630303715</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>84.49134766649186</v>
+        <v>89.3526654950205</v>
       </c>
       <c r="D3" t="n">
-        <v>139.6043810438838</v>
+        <v>156.1137900904475</v>
       </c>
     </row>
     <row r="4">
@@ -497,10 +497,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>86.43156790770843</v>
+        <v>90.62683069712946</v>
       </c>
       <c r="D4" t="n">
-        <v>146.2115685125011</v>
+        <v>160.6292165488852</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>70.00524383848978</v>
+        <v>73.59402460456943</v>
       </c>
       <c r="D5" t="n">
-        <v>95.28236293754347</v>
+        <v>108.6817244375801</v>
       </c>
     </row>
     <row r="6">
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>70.64761405348716</v>
+        <v>74.5459871118922</v>
       </c>
       <c r="D6" t="n">
-        <v>98.14028208756929</v>
+        <v>112.2020817896597</v>
       </c>
     </row>
     <row r="7">
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>76.58626114315679</v>
+        <v>81.57586408904511</v>
       </c>
       <c r="D7" t="n">
-        <v>117.4579771771344</v>
+        <v>134.1693868397511</v>
       </c>
     </row>
     <row r="8">
@@ -562,10 +562,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>87.55899318300996</v>
+        <v>91.56414762741653</v>
       </c>
       <c r="D8" t="n">
-        <v>149.4355157552812</v>
+        <v>163.4045533971569</v>
       </c>
     </row>
   </sheetData>

--- a/modeling/data/argentina/df_modelos.xlsx
+++ b/modeling/data/argentina/df_modelos.xlsx
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>86.14528412419449</v>
+        <v>76.63099758370728</v>
       </c>
       <c r="D2" t="n">
-        <v>148.301630303715</v>
+        <v>106.6817938003297</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>89.3526654950205</v>
+        <v>79.51328960994132</v>
       </c>
       <c r="D3" t="n">
-        <v>156.1137900904475</v>
+        <v>114.9172097478617</v>
       </c>
     </row>
     <row r="4">
@@ -497,10 +497,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>90.62683069712946</v>
+        <v>76.5792198826372</v>
       </c>
       <c r="D4" t="n">
-        <v>160.6292165488852</v>
+        <v>106.7061293198326</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>73.59402460456943</v>
+        <v>60.06213324128409</v>
       </c>
       <c r="D5" t="n">
-        <v>108.6817244375801</v>
+        <v>61.94883182308163</v>
       </c>
     </row>
     <row r="6">
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>74.5459871118922</v>
+        <v>59.80324473593373</v>
       </c>
       <c r="D6" t="n">
-        <v>112.2020817896597</v>
+        <v>61.18597369398256</v>
       </c>
     </row>
     <row r="7">
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>81.57586408904511</v>
+        <v>75.26751812219538</v>
       </c>
       <c r="D7" t="n">
-        <v>134.1693868397511</v>
+        <v>108.6723012218</v>
       </c>
     </row>
     <row r="8">
@@ -562,10 +562,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>91.56414762741653</v>
+        <v>76.83810838798757</v>
       </c>
       <c r="D8" t="n">
-        <v>163.4045533971569</v>
+        <v>110.6985352570089</v>
       </c>
     </row>
   </sheetData>

--- a/modeling/data/argentina/df_modelos.xlsx
+++ b/modeling/data/argentina/df_modelos.xlsx
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>76.63099758370728</v>
+        <v>78.1681497391838</v>
       </c>
       <c r="D2" t="n">
-        <v>106.6817938003297</v>
+        <v>113.306326183763</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>79.51328960994132</v>
+        <v>81.60478674440012</v>
       </c>
       <c r="D3" t="n">
-        <v>114.9172097478617</v>
+        <v>117.7882398670104</v>
       </c>
     </row>
     <row r="4">
@@ -497,10 +497,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>76.5792198826372</v>
+        <v>83.26173672905799</v>
       </c>
       <c r="D4" t="n">
-        <v>106.7061293198326</v>
+        <v>124.3615578499184</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>60.06213324128409</v>
+        <v>70.69653267873581</v>
       </c>
       <c r="D5" t="n">
-        <v>61.94883182308163</v>
+        <v>87.6195024258663</v>
       </c>
     </row>
     <row r="6">
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>59.80324473593373</v>
+        <v>71.80116600184105</v>
       </c>
       <c r="D6" t="n">
-        <v>61.18597369398256</v>
+        <v>89.18890596114133</v>
       </c>
     </row>
     <row r="7">
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>75.26751812219538</v>
+        <v>73.94906413010125</v>
       </c>
       <c r="D7" t="n">
-        <v>108.6723012218</v>
+        <v>99.9849775336242</v>
       </c>
     </row>
     <row r="8">
@@ -562,10 +562,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>76.83810838798757</v>
+        <v>84.70389690088984</v>
       </c>
       <c r="D8" t="n">
-        <v>110.6985352570089</v>
+        <v>129.0201989169002</v>
       </c>
     </row>
   </sheetData>

--- a/modeling/data/argentina/df_modelos.xlsx
+++ b/modeling/data/argentina/df_modelos.xlsx
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>78.1681497391838</v>
+        <v>80.21761929732564</v>
       </c>
       <c r="D2" t="n">
-        <v>113.306326183763</v>
+        <v>130.7065948817072</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>81.60478674440012</v>
+        <v>84.07184058730991</v>
       </c>
       <c r="D3" t="n">
-        <v>117.7882398670104</v>
+        <v>138.649840465643</v>
       </c>
     </row>
     <row r="4">
@@ -497,10 +497,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>83.26173672905799</v>
+        <v>86.44467750393288</v>
       </c>
       <c r="D4" t="n">
-        <v>124.3615578499184</v>
+        <v>146.8817492228531</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>70.69653267873581</v>
+        <v>69.67750393287886</v>
       </c>
       <c r="D5" t="n">
-        <v>87.6195024258663</v>
+        <v>96.08553283167313</v>
       </c>
     </row>
     <row r="6">
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>71.80116600184105</v>
+        <v>71.05401153644468</v>
       </c>
       <c r="D6" t="n">
-        <v>89.18890596114133</v>
+        <v>101.1019273129745</v>
       </c>
     </row>
     <row r="7">
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>73.94906413010125</v>
+        <v>76.50760356581017</v>
       </c>
       <c r="D7" t="n">
-        <v>99.9849775336242</v>
+        <v>118.0648902821085</v>
       </c>
     </row>
     <row r="8">
@@ -562,10 +562,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>84.70389690088984</v>
+        <v>87.00839014158365</v>
       </c>
       <c r="D8" t="n">
-        <v>129.0201989169002</v>
+        <v>148.5073290190958</v>
       </c>
     </row>
   </sheetData>

--- a/modeling/data/argentina/df_modelos.xlsx
+++ b/modeling/data/argentina/df_modelos.xlsx
@@ -451,14 +451,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DecisionTreeClassifier(max_depth=30)</t>
+          <t>DecisionTreeClassifier(max_depth=28)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>48.07516040329973</v>
+        <v>53.05951383067895</v>
       </c>
       <c r="D2" t="n">
-        <v>38.32263978001836</v>
+        <v>51.68762224084941</v>
       </c>
     </row>
     <row r="3">
@@ -467,14 +467,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RandomForestClassifier(n_estimators=200, random_state=42)</t>
+          <t>RandomForestClassifier(max_depth=15, random_state=42)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>53.25389550870761</v>
+        <v>55.35065660799106</v>
       </c>
       <c r="D3" t="n">
-        <v>44.05637030247475</v>
+        <v>53.58507963118186</v>
       </c>
     </row>
     <row r="4">
@@ -490,17 +490,17 @@
               gamma=None, gpu_id=None, grow_policy=None, importance_type=None,
               interaction_constraints=None, learning_rate=None, max_bin=None,
               max_cat_threshold=None, max_cat_to_onehot=None,
-              max_delta_step=None, max_depth=20, max_leaves=None,
+              max_delta_step=None, max_depth=25, max_leaves=None,
               min_child_weight=None, missing=nan, monotone_constraints=None,
               n_estimators=50, n_jobs=None, num_class=3, num_parallel_tree=None,
               objective='multi:softmax', ...)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>51.28322639780018</v>
+        <v>55.07124895222129</v>
       </c>
       <c r="D4" t="n">
-        <v>42.53941338221813</v>
+        <v>54.79407655769766</v>
       </c>
     </row>
     <row r="5">
@@ -509,14 +509,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LogisticRegression(C=0.1, max_iter=500, multi_class='multinomial')</t>
+          <t>LogisticRegression(C=0.1, multi_class='multinomial', penalty=None)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>42.25481209899175</v>
+        <v>40.1229393685387</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8235563703024448</v>
+        <v>-6.998602961721114</v>
       </c>
     </row>
     <row r="6">
@@ -525,14 +525,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVC(decision_function_shape='ovo')</t>
+          <t>SVC(decision_function_shape='ovo', kernel='linear')</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>41.9340054995417</v>
+        <v>39.56412405699916</v>
       </c>
       <c r="D6" t="n">
-        <v>4.335930339138391</v>
+        <v>-8.483654652137416</v>
       </c>
     </row>
     <row r="7">
@@ -541,15 +541,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MLPClassifier(activation='tanh', hidden_layer_sizes=128,
-              learning_rate='invscaling', max_iter=300)</t>
+          <t>MLPClassifier(activation='tanh', hidden_layer_sizes=(64, 32),
+              learning_rate='adaptive', max_iter=300, solver='lbfgs')</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.33363886342805</v>
+        <v>50.71248952221291</v>
       </c>
       <c r="D7" t="n">
-        <v>28.58020164986251</v>
+        <v>45.06901369097515</v>
       </c>
     </row>
     <row r="8">
@@ -558,14 +558,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GradientBoostingClassifier(max_depth=7, n_estimators=200)</t>
+          <t>GradientBoostingClassifier(learning_rate=0.05, max_depth=7, n_estimators=300)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50.91659028414298</v>
+        <v>55.32271584241408</v>
       </c>
       <c r="D8" t="n">
-        <v>40.98716773602199</v>
+        <v>55.84800223526128</v>
       </c>
     </row>
   </sheetData>
